--- a/SGC-CKN/Excel/a384775f-efcd-483e-8624-b927b1d1c14f_Lô_CT-02_P1-74_D800_29-03-2026.xlsx
+++ b/SGC-CKN/Excel/a384775f-efcd-483e-8624-b927b1d1c14f_Lô_CT-02_P1-74_D800_29-03-2026.xlsx
@@ -1371,16 +1371,16 @@
         <v>-25.9</v>
       </c>
       <c r="G17" s="25">
-        <v>-35.4</v>
+        <v>-35.44</v>
       </c>
       <c r="H17" s="25">
         <v>1</v>
       </c>
       <c r="I17" s="25">
-        <v>9.5</v>
+        <v>9.54</v>
       </c>
       <c r="J17" s="8">
-        <v>9.5</v>
+        <v>9.54</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>50</v>
@@ -1403,7 +1403,7 @@
         <v>54</v>
       </c>
       <c r="F18" s="28">
-        <v>-35.4</v>
+        <v>-35.44</v>
       </c>
       <c r="G18" s="28">
         <v>-44.21</v>
@@ -1412,10 +1412,10 @@
         <v>1.72</v>
       </c>
       <c r="I18" s="28">
-        <v>8.81</v>
+        <v>8.77</v>
       </c>
       <c r="J18" s="8">
-        <v>5.13</v>
+        <v>5.11</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>55</v>
@@ -1747,16 +1747,16 @@
         <v>-25.9</v>
       </c>
       <c r="F8" s="25">
-        <v>-35.4</v>
+        <v>-35.44</v>
       </c>
       <c r="G8" s="25">
         <v>1</v>
       </c>
       <c r="H8" s="25">
-        <v>9.5</v>
+        <v>9.54</v>
       </c>
       <c r="I8" s="8">
-        <v>9.5</v>
+        <v>9.54</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1773,7 +1773,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-35.4</v>
+        <v>-35.44</v>
       </c>
       <c r="F9" s="28">
         <v>-44.21</v>
@@ -1782,10 +1782,10 @@
         <v>1.72</v>
       </c>
       <c r="H9" s="28">
-        <v>8.81</v>
+        <v>8.77</v>
       </c>
       <c r="I9" s="8">
-        <v>5.13</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
